--- a/src/beastmistress/assets/data/elements.xlsx
+++ b/src/beastmistress/assets/data/elements.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="120" windowWidth="22020" windowHeight="9024"/>
+    <workbookView xWindow="384" yWindow="120" windowWidth="22020" windowHeight="9024" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="elements" sheetId="1" r:id="rId1"/>
+    <sheet name="dualElements" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
   <si>
     <t>Water</t>
   </si>
@@ -50,6 +51,90 @@
   </si>
   <si>
     <t>Strong</t>
+  </si>
+  <si>
+    <t>Plus…</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>Swamp</t>
+  </si>
+  <si>
+    <t>Breeze</t>
+  </si>
+  <si>
+    <t>Twilight</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Frost</t>
+  </si>
+  <si>
+    <t>Chill</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Mercury</t>
+  </si>
+  <si>
+    <t>Coldfire</t>
+  </si>
+  <si>
+    <t>Hellfire</t>
+  </si>
+  <si>
+    <t>Blessed</t>
+  </si>
+  <si>
+    <t>Pure</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Hurricane</t>
+  </si>
+  <si>
+    <t>Helium</t>
+  </si>
+  <si>
+    <t>Blizzard</t>
+  </si>
+  <si>
+    <t>Blast</t>
+  </si>
+  <si>
+    <t>Lava</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Cursed</t>
+  </si>
+  <si>
+    <t>Permafrost</t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>Tainted</t>
+  </si>
+  <si>
+    <t>Sacred</t>
   </si>
 </sst>
 </file>
@@ -65,12 +150,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -113,15 +204,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="106">
+  <dxfs count="31">
     <dxf>
       <fill>
         <patternFill>
@@ -174,6 +266,153 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
@@ -182,678 +421,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1432,40 +999,285 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I9">
-    <cfRule type="cellIs" dxfId="102" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
       <formula>"Weak"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
       <formula>"Strong"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
       <formula>"Neutral"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="cellIs" dxfId="77" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
       <formula>"Water"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>"Earth"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
       <formula>"Air"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>"Fire"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"Ice"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"Metal"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"Dark"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A9">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Dark"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"Metal"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"Ice"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"Fire"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"Air"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>"Earth"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"Water"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:I1">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Dark"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Metal"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Ice"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Fire"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Air"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Earth"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"Water"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/beastmistress/assets/data/elements.xlsx
+++ b/src/beastmistress/assets/data/elements.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="41">
   <si>
     <t>Water</t>
   </si>
@@ -56,15 +56,6 @@
     <t>Plus…</t>
   </si>
   <si>
-    <t>Rain</t>
-  </si>
-  <si>
-    <t>Swamp</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
     <t>Twilight</t>
   </si>
   <si>
@@ -74,18 +65,9 @@
     <t>Silver</t>
   </si>
   <si>
-    <t>Frost</t>
-  </si>
-  <si>
-    <t>Chill</t>
-  </si>
-  <si>
     <t>Iron</t>
   </si>
   <si>
-    <t>Mercury</t>
-  </si>
-  <si>
     <t>Coldfire</t>
   </si>
   <si>
@@ -107,34 +89,55 @@
     <t>Helium</t>
   </si>
   <si>
-    <t>Blizzard</t>
-  </si>
-  <si>
-    <t>Blast</t>
-  </si>
-  <si>
     <t>Lava</t>
   </si>
   <si>
-    <t>Oil</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
     <t>Cursed</t>
   </si>
   <si>
-    <t>Permafrost</t>
-  </si>
-  <si>
-    <t>Rock</t>
-  </si>
-  <si>
     <t>Tainted</t>
   </si>
   <si>
     <t>Sacred</t>
+  </si>
+  <si>
+    <t>Bogged</t>
+  </si>
+  <si>
+    <t>Static</t>
+  </si>
+  <si>
+    <t>Oily</t>
+  </si>
+  <si>
+    <t>Frosty</t>
+  </si>
+  <si>
+    <t>Mercurial</t>
+  </si>
+  <si>
+    <t>Breezy</t>
+  </si>
+  <si>
+    <t>Slippery</t>
+  </si>
+  <si>
+    <t>Rocky</t>
+  </si>
+  <si>
+    <t>Explosive</t>
+  </si>
+  <si>
+    <t>Chilly</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Aquamarine</t>
   </si>
 </sst>
 </file>
@@ -213,102 +216,53 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -999,36 +953,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I9">
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
       <formula>"Weak"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="9" operator="equal">
       <formula>"Strong"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
       <formula>"Neutral"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I9">
-    <cfRule type="cellIs" dxfId="27" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>"Water"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"Earth"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
       <formula>"Air"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"Fire"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>"Ice"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Metal"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"Dark"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1089,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1104,10 +1058,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -1121,13 +1075,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1140,16 +1094,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -1161,19 +1115,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1184,22 +1138,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1209,72 +1163,72 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I9" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A9">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
       <formula>"Dark"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>"Metal"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"Ice"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"Fire"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"Air"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
       <formula>"Earth"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"Water"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:I1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"Dark"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"Metal"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"Ice"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"Fire"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"Air"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"Earth"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Water"</formula>
     </cfRule>
   </conditionalFormatting>
